--- a/execution-substrates/csv/rulebook.xlsx
+++ b/execution-substrates/csv/rulebook.xlsx
@@ -459,7 +459,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -506,7 +506,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>CountOfSteps</t>
+          <t>CountOfNonProposedSteps</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -518,186 +518,186 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>onboarding</t>
+          <t>performance-review</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>onboarding</t>
+          <t>performance-review</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Performance Review</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Employee Onboarding</t>
+          <t>Annual Performance Review</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>A step-by-step process to onboard new employees, including document collection, orientation, and training.</t>
+          <t>Structured workflow for conducting annual employee performance evaluations.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>WF-ONB-001</t>
+          <t>WF-PRV-007</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>submit-request</t>
+          <t>system-notification-sent, step-2, recwwXHLqxKPhj6Mt</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="3" t="b">
         <v>1</v>
-      </c>
-      <c r="J2" s="3" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>invoice-approval</t>
+          <t>change-management</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>invoice-approval</t>
+          <t>change-management</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Invoice Approval</t>
+          <t>Change Management</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Invoice Approval Workflow</t>
+          <t>Change Management Workflow</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Automated workflow for reviewing, approving, and processing vendor invoices.</t>
+          <t>Structured process for requesting, evaluating, and implementing organizational changes.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>WF-INV-002</t>
+          <t>WF-CHM-015</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>manager-review</t>
+          <t>close-workflow, step1, asdf</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="3" t="b">
         <v>1</v>
-      </c>
-      <c r="J3" s="3" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>content-publishing</t>
+          <t>asset-management</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>content-publishing</t>
+          <t>asset-management</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Content Publishing</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Content Publishing Process</t>
+          <t>Asset Management Process</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Workflow for drafting, reviewing, and publishing content to the company website.</t>
+          <t>Process for tracking, maintaining, and auditing company assets.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>WF-CNT-003</t>
+          <t>WF-ASM-012</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>automated-eligibility-check</t>
+          <t>assign-task-to-team, some-new-task</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3" t="b">
         <v>1</v>
-      </c>
-      <c r="J4" s="3" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>leave-request</t>
+          <t>incident-reporting</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>leave-request</t>
+          <t>incident-reporting</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Leave Request</t>
+          <t>Incident Reporting</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Leave Request Workflow</t>
+          <t>Incident Reporting Process</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Process for employees to submit, review, and approve leave requests.</t>
+          <t>Steps for reporting, investigating, and resolving workplace incidents.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>WF-LRQ-004</t>
+          <t>WF-INC-014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>finance-approval</t>
+          <t>generate-report</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
@@ -710,42 +710,42 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>it-support</t>
+          <t>customer-feedback</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>it-support</t>
+          <t>customer-feedback</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>IT Support</t>
+          <t>Customer Feedback</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>IT Support Ticketing</t>
+          <t>Customer Feedback Collection</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Workflow for submitting, triaging, and resolving IT support tickets.</t>
+          <t>Workflow for collecting, analyzing, and acting on customer feedback.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>WF-ITS-005</t>
+          <t>WF-CFB-009</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>document-verification</t>
+          <t>archive-request</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
@@ -758,42 +758,42 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>expense-reimbursement</t>
+          <t>project-kickoff</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>expense-reimbursement</t>
+          <t>project-kickoff</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Expense Reimbursement</t>
+          <t>Project Kickoff</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Expense Reimbursement Process</t>
+          <t>Project Kickoff Process</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Steps for employees to submit expenses and receive reimbursements after approval.</t>
+          <t>Steps to initiate a new project, including team assignment and goal setting.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>WF-EXP-006</t>
+          <t>WF-PKO-010</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>quality-assurance-review</t>
+          <t>customer-feedback-collection</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
@@ -806,42 +806,42 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>performance-review</t>
+          <t>onboarding</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>performance-review</t>
+          <t>onboarding</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Performance Review</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Annual Performance Review</t>
+          <t>Employee Onboarding</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Structured workflow for conducting annual employee performance evaluations.</t>
+          <t>A step-by-step process to onboard new employees, including document collection, orientation, and training.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>WF-PRV-007</t>
+          <t>WF-ONB-001</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>system-notification-sent</t>
+          <t>submit-request</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
@@ -854,42 +854,42 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>procurement</t>
+          <t>content-publishing</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>procurement</t>
+          <t>content-publishing</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Content Publishing</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Procurement Workflow</t>
+          <t>Content Publishing Process</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Process for requesting, approving, and purchasing goods or services.</t>
+          <t>Workflow for drafting, reviewing, and publishing content to the company website.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>WF-PRC-008</t>
+          <t>WF-CNT-003</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>final-approval</t>
+          <t>automated-eligibility-check</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
@@ -902,42 +902,42 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>customer-feedback</t>
+          <t>expense-reimbursement</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>customer-feedback</t>
+          <t>expense-reimbursement</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Customer Feedback</t>
+          <t>Expense Reimbursement</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Customer Feedback Collection</t>
+          <t>Expense Reimbursement Process</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Workflow for collecting, analyzing, and acting on customer feedback.</t>
+          <t>Steps for employees to submit expenses and receive reimbursements after approval.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>WF-CFB-009</t>
+          <t>WF-EXP-006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>archive-request</t>
+          <t>quality-assurance-review</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
@@ -950,42 +950,42 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>project-kickoff</t>
+          <t>procurement</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>project-kickoff</t>
+          <t>procurement</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Project Kickoff</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Project Kickoff Process</t>
+          <t>Procurement Workflow</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Steps to initiate a new project, including team assignment and goal setting.</t>
+          <t>Process for requesting, approving, and purchasing goods or services.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>WF-PKO-010</t>
+          <t>WF-PRC-008</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>customer-feedback-collection</t>
+          <t>final-approval</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
@@ -998,42 +998,42 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>contract-review</t>
+          <t>invoice-approval</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>contract-review</t>
+          <t>invoice-approval</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Contract Review</t>
+          <t>Invoice Approval</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Contract Review Workflow</t>
+          <t>Invoice Approval Workflow</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Workflow for legal and management review of contracts before signing.</t>
+          <t>Automated workflow for reviewing, approving, and processing vendor invoices.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>WF-CTR-011</t>
+          <t>WF-INV-002</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>legal-compliance-check</t>
+          <t>manager-review</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
@@ -1046,49 +1046,49 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>asset-management</t>
+          <t>contract-review</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>asset-management</t>
+          <t>contract-review</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>Contract Review</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Asset Management Process</t>
+          <t>Contract Review Workflow</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Process for tracking, maintaining, and auditing company assets.</t>
+          <t>Workflow for legal and management review of contracts before signing.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>WF-ASM-012</t>
+          <t>WF-CTR-011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>assign-task-to-team, some-new-task</t>
+          <t>legal-compliance-check</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1142,42 +1142,42 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>incident-reporting</t>
+          <t>it-support</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>incident-reporting</t>
+          <t>it-support</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Incident Reporting</t>
+          <t>IT Support</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Incident Reporting Process</t>
+          <t>IT Support Ticketing</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Steps for reporting, investigating, and resolving workplace incidents.</t>
+          <t>Workflow for submitting, triaging, and resolving IT support tickets.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>WF-INC-014</t>
+          <t>WF-ITS-005</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>generate-report</t>
+          <t>document-verification</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
@@ -1190,42 +1190,42 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>change-management</t>
+          <t>leave-request</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>change-management</t>
+          <t>leave-request</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Change Management</t>
+          <t>Leave Request</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Change Management Workflow</t>
+          <t>Leave Request Workflow</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Structured process for requesting, evaluating, and implementing organizational changes.</t>
+          <t>Process for employees to submit, review, and approve leave requests.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>WF-CHM-015</t>
+          <t>WF-LRQ-004</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>close-workflow</t>
+          <t>finance-approval</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
@@ -1246,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1396,331 +1396,311 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>automated-eligibility-check</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>automated-eligibility-check</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Automated Eligibility Check</t>
-        </is>
-      </c>
+          <t>recwwXHLqxKPhj6Mt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>content-publishing</t>
+          <t>performance-review</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>viewer</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>it-security-gate</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>step-3</t>
-        </is>
-      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>finance-approval</t>
+          <t>automated-eligibility-check</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>finance-approval</t>
+          <t>automated-eligibility-check</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Finance Approval</t>
+          <t>Automated Eligibility Check</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>leave-request</t>
+          <t>content-publishing</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>moderator</t>
+          <t>viewer</t>
         </is>
       </c>
       <c r="G5" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>finance-approval</t>
+          <t>it-security-gate</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>step-4</t>
+          <t>step-3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>document-verification</t>
+          <t>finance-approval</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>document-verification</t>
+          <t>finance-approval</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Document Verification</t>
+          <t>Finance Approval</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>it-support</t>
+          <t>leave-request</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>contributor</t>
+          <t>moderator</t>
         </is>
       </c>
       <c r="G6" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>compliance-check</t>
+          <t>finance-approval</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>step-5</t>
+          <t>step-4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>quality-assurance-review</t>
+          <t>document-verification</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>quality-assurance-review</t>
+          <t>document-verification</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Quality Assurance Review</t>
+          <t>Document Verification</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>expense-reimbursement</t>
+          <t>it-support</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>contributor</t>
         </is>
       </c>
       <c r="G7" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>quality-assurance</t>
+          <t>compliance-check</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>step-6</t>
+          <t>step-5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>system-notification-sent</t>
+          <t>quality-assurance-review</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>system-notification-sent</t>
+          <t>quality-assurance-review</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>System Notification Sent</t>
+          <t>Quality Assurance Review</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>performance-review</t>
+          <t>expense-reimbursement</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="G8" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>final-authorization</t>
+          <t>quality-assurance</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>step-7</t>
+          <t>step-6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>final-approval</t>
+          <t>system-notification-sent</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>final-approval</t>
+          <t>system-notification-sent</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Final Approval</t>
+          <t>System Notification Sent</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>procurement</t>
+          <t>performance-review</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>analyst</t>
+          <t>support</t>
         </is>
       </c>
       <c r="G9" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>manager-approval</t>
+          <t>final-authorization</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>step-8</t>
+          <t>step-7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>archive-request</t>
+          <t>final-approval</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>archive-request</t>
+          <t>final-approval</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Archive Request</t>
+          <t>Final Approval</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>customer-feedback</t>
+          <t>procurement</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>developer</t>
+          <t>analyst</t>
         </is>
       </c>
       <c r="G10" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>it-security-gate</t>
+          <t>manager-approval</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>step-9</t>
+          <t>step-8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>customer-feedback-collection</t>
+          <t>archive-request</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>customer-feedback-collection</t>
+          <t>archive-request</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Customer Feedback Collection</t>
+          <t>Archive Request</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>project-kickoff</t>
+          <t>customer-feedback</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>tester</t>
+          <t>developer</t>
         </is>
       </c>
       <c r="G11" s="2" t="b">
@@ -1728,115 +1708,115 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>customer-confirmation</t>
+          <t>it-security-gate</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>step-10</t>
+          <t>step-9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>legal-compliance-check</t>
+          <t>customer-feedback-collection</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>legal-compliance-check</t>
+          <t>customer-feedback-collection</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Legal Compliance Check</t>
+          <t>Customer Feedback Collection</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>contract-review</t>
+          <t>project-kickoff</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>tester</t>
         </is>
       </c>
       <c r="G12" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>legal-review</t>
+          <t>customer-confirmation</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>step-11</t>
+          <t>step-10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>assign-task-to-team</t>
+          <t>legal-compliance-check</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>assign-task-to-team</t>
+          <t>legal-compliance-check</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Assign Task to Team</t>
+          <t>Legal Compliance Check</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>asset-management</t>
+          <t>contract-review</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="G13" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>executive-sign-off</t>
+          <t>legal-review</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>step-12</t>
+          <t>step-11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>some-new-task</t>
+          <t>assign-task-to-team</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>some-new-task</t>
+          <t>assign-task-to-team</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Some new task</t>
+          <t>Assign Task to Team</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1845,7 +1825,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1857,34 +1837,34 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>some-new-gate</t>
+          <t>executive-sign-off</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>assign-task-to-team</t>
+          <t>step-12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>team-lead-review</t>
+          <t>some-new-task</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>team-lead-review</t>
+          <t>some-new-task</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Team Lead Review</t>
+          <t>Some new task</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>recruitment</t>
+          <t>asset-management</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -1892,93 +1872,93 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>guest</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="G15" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>legal-review</t>
+          <t>some-new-gate</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>step-13</t>
+          <t>assign-task-to-team</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>generate-report</t>
+          <t>team-lead-review</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>generate-report</t>
+          <t>team-lead-review</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Generate Report</t>
+          <t>Team Lead Review</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>incident-reporting</t>
+          <t>recruitment</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>trainer</t>
+          <t>guest</t>
         </is>
       </c>
       <c r="G16" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>finance-approval</t>
+          <t>legal-review</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>step-14</t>
+          <t>step-13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>close-workflow</t>
+          <t>generate-report</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>close-workflow</t>
+          <t>generate-report</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Close Workflow</t>
+          <t>Generate Report</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>change-management</t>
+          <t>incident-reporting</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>trainer</t>
         </is>
       </c>
       <c r="G17" s="2" t="b">
@@ -1986,14 +1966,150 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>step-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Close Workflow</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>executive-sign-off</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>step-15</t>
         </is>
       </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>step1</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>step1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>step1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>asdf</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>asdf</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>asdf</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2334,9 +2450,9 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2352,17 +2468,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>WorkflowStep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>DisplayName</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>StepNumber</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>WorkflowStep</t>
         </is>
       </c>
     </row>
@@ -2377,18 +2493,18 @@
           <t>step-1</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Step-1</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="E2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>submit-request</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -2402,18 +2518,18 @@
           <t>step-2</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Step-2</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="E3" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>manager-review</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -2427,18 +2543,18 @@
           <t>step-3</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Step-3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>automated-eligibility-check</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -2452,18 +2568,18 @@
           <t>step-4</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Step-4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="E5" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>finance-approval</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -2477,18 +2593,18 @@
           <t>step-5</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Step-5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="E6" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>document-verification</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -2502,18 +2618,18 @@
           <t>step-6</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Step-6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="E7" s="2" t="n">
         <v>6</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>quality-assurance-review</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -2527,18 +2643,18 @@
           <t>step-7</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Step-7</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="E8" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>system-notification-sent</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -2552,18 +2668,18 @@
           <t>step-8</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Step-8</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>8</v>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>final-approval</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -2577,18 +2693,18 @@
           <t>step-9</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Step-9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="E10" s="2" t="n">
         <v>9</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>archive-request</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -2602,18 +2718,18 @@
           <t>step-10</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Step-10</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="E11" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>customer-feedback-collection</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -2627,18 +2743,18 @@
           <t>step-11</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Step-11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="E12" s="2" t="n">
         <v>11</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>legal-compliance-check</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -2652,18 +2768,18 @@
           <t>step-12</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Step-12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="E13" s="2" t="n">
         <v>12</v>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>assign-task-to-team</t>
-        </is>
       </c>
     </row>
     <row r="14">
@@ -2677,18 +2793,18 @@
           <t>step-13</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Step-13</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="E14" s="2" t="n">
         <v>13</v>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>team-lead-review</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -2702,18 +2818,18 @@
           <t>step-14</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Step-14</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="E15" s="2" t="n">
         <v>14</v>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>generate-report</t>
-        </is>
       </c>
     </row>
     <row r="16">
@@ -2727,18 +2843,18 @@
           <t>step-15</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Step-15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="E16" s="2" t="n">
         <v>15</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>close-workflow</t>
-        </is>
       </c>
     </row>
     <row r="17">
@@ -2752,18 +2868,18 @@
           <t>assign-task-to-team</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Step-16</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="E17" s="2" t="n">
         <v>16</v>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>some-new-task</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/execution-substrates/csv/rulebook.xlsx
+++ b/execution-substrates/csv/rulebook.xlsx
@@ -7,7 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Workflows" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WorkflowSteps" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ApprovalGates" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PrecedesSteps" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Roles" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Departments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="HumanAgents" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="AIAgents" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="AutomatedPipelines" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,142 +448,5342 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowSteps</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CountOfNonProposedSteps</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>HasMoreThan1Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Performance Review</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Annual Performance Review</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Structured workflow for conducting annual employee performance evaluations.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>WF-PRV-007</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent, step-2, recwwXHLqxKPhj6Mt</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Change Management</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Change Management Workflow</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Structured process for requesting, evaluating, and implementing organizational changes.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>WF-CHM-015</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow, step1, asdf</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>asset-management</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>asset-management</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Asset Management</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Asset Management Process</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Process for tracking, maintaining, and auditing company assets.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>WF-ASM-012</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team, some-new-task</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>incident-reporting</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>incident-reporting</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Incident Reporting</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Incident Reporting Process</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Steps for reporting, investigating, and resolving workplace incidents.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>WF-INC-014</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>customer-feedback</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Customer Feedback</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Customer Feedback Collection</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for collecting, analyzing, and acting on customer feedback.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>WF-CFB-009</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>project-kickoff</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>project-kickoff</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Project Kickoff</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Project Kickoff Process</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Steps to initiate a new project, including team assignment and goal setting.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>WF-PKO-010</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>onboarding</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>onboarding</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Employee Onboarding</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>A step-by-step process to onboard new employees, including document collection, orientation, and training.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>WF-ONB-001</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>content-publishing</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>content-publishing</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Content Publishing</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Content Publishing Process</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for drafting, reviewing, and publishing content to the company website.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>WF-CNT-003</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>expense-reimbursement</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>expense-reimbursement</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Expense Reimbursement</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Expense Reimbursement Process</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Steps for employees to submit expenses and receive reimbursements after approval.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>WF-EXP-006</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Workflow</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Process for requesting, approving, and purchasing goods or services.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>WF-PRC-008</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>invoice-approval</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>invoice-approval</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Approval</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Approval Workflow</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Automated workflow for reviewing, approving, and processing vendor invoices.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>WF-INV-002</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>contract-review</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>contract-review</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Contract Review</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Contract Review Workflow</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for legal and management review of contracts before signing.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>WF-CTR-011</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment Workflow</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for posting jobs, screening candidates, and scheduling interviews.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>WF-RCT-013</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>it-support</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>it-support</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>IT Support</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>IT Support Ticketing</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Workflow for submitting, triaging, and resolving IT support tickets.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>WF-ITS-005</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>leave-request</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>leave-request</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Leave Request</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Leave Request Workflow</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Process for employees to submit, review, and approve leave requests.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>WF-LRQ-004</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowStepId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SequencePosition</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>AssignedRole</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RequiresHumanApproval</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovalGate</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>PrecededBySteps</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Submit Request</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>onboarding</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>initial-review</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>step-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Manager Review</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>invoice-approval</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>manager-approval</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>recwwXHLqxKPhj6Mt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Automated Eligibility Check</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>content-publishing</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>it-security-gate</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>step-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Finance Approval</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>leave-request</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>step-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Document Verification</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>it-support</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>compliance-check</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>step-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance Review</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>expense-reimbursement</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>step-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>System Notification Sent</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>final-authorization</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>step-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Final Approval</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>manager-approval</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>step-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Archive Request</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>it-security-gate</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>step-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Customer Feedback Collection</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>project-kickoff</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>customer-confirmation</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>step-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Legal Compliance Check</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>contract-review</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>legal-review</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>step-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Assign Task to Team</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>asset-management</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>executive-sign-off</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>step-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Some new task</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>asset-management</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>some-new-gate</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Team Lead Review</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>recruitment</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>legal-review</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>step-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Generate Report</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>incident-reporting</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>step-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Close Workflow</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>executive-sign-off</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>step-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>step1</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>step1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>step1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>asdf</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>asdf</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>asdf</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>change-management</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Step 2</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>performance-review</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovalGateId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowSteps</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>EscalationThresholdHours</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>initial-review</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>initial-review</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Initial Review</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>manager-approval</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>manager-approval</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Manager Approval</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>final-approval, manager-review</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>compliance-check</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>compliance-check</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Compliance Check</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>final-authorization</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>final-authorization</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Final Authorization</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>executive-sign-off</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>executive-sign-off</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Executive Sign-off</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow, assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>legal-review</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>legal-review</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Legal Review</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review, legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Finance Approval</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>generate-report, finance-approval</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>it-security-gate</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>it-security-gate</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>IT Security Gate</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>archive-request, automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>customer-confirmation</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>customer-confirmation</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Customer Confirmation</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>some-new-gate</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>some-new-gate</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>some new gate</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PrecedesStepId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowStep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>StepNumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>step-1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>step-1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Step-1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>step-2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Step-2</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>step-3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>step-3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Step-3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>step-4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>step-4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Step-4</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>step-5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>step-5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Step-5</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>step-6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>step-6</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Step-6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>step-7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>step-7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Step-7</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>step-8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>step-8</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Step-8</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>step-9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>step-9</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Step-9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>step-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>step-10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Step-10</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>step-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>step-11</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Step-11</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>step-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>step-12</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Step-12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>step-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>step-13</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Step-13</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>step-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>step-14</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Step-14</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>step-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>step-15</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Step-15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>some-new-task</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Step-16</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RoleId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>FilledByHumanAgent</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>FilledByAIAgent</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FilledByAutomatedPipeline</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>OwnedBy</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>DelegatesTo</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WorkflowSteps</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>FromDelegatesTo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Has full access to all system features and settings.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>agent-001</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>ava</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>lead-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>human-resources</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>submit-request</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Editor</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Content Editor</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Can create, edit, and delete content but cannot change system settings.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>agent-002</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>leo</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>e-commerce-order-sync</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>manager-review</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Viewer</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Can view content but cannot make any changes.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>agent-003</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>maya</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>issue-tracking-bridge</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>information-technology</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>automated-eligibility-check</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Moderator</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Forum Moderator</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Can manage user comments and moderate discussions.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>agent-004</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>newsletter-signup-sync</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>finance-approval</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Contributor</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Content Contributor</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Can submit new content for review but cannot publish directly.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>agent-005</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>zara</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>support-ticket-automation</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>document-verification</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Oversees project progress and manages team assignments.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>agent-006</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>owen</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>devops-integration</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>customer-service</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance-review</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Handles user inquiries and provides technical assistance.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>agent-007</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>nina</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>finance-automation</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>research-and-development</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>system-notification-sent</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Has access to analytics and reporting tools.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>agent-008</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>kai</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>project-intake-pipeline</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>final-approval</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Can access and modify application code and integrations.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>agent-009</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>sophie</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>crm-data-sync</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>archive-request</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Responsible for testing new features and reporting bugs.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>agent-010</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>calendar-integration</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>customer-feedback-collection</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Manages employee records and recruitment processes.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>agent-011</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>liam</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-pipeline</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>legal-compliance-check</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Finance Officer</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Handles billing, invoices, and financial reports.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>agent-012</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>jade</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>task-management-sync</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>public-relations</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>assign-task-to-team, some-new-task</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Temporary Access</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Limited access for temporary users or external collaborators.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>agent-013</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>mila</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>cloud-storage-sync</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>team-lead-review</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Training Specialist</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Creates and delivers training materials to users.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>agent-014</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>noah</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>email-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>facilities-management</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>generate-report</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>System Owner</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Ultimate authority over the system, can assign or revoke any role.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>agent-015</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>ella</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-export</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>training-and-development</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>close-workflow</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DepartmentId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>human-resources</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>human-resources</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>HR Department</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Finance Department</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>information-technology</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>information-technology</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>IT Department</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Department</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Sales Department</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>customer-service</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>customer-service</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Service Department</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Service</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>research-and-development</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>research-and-development</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>R&amp;D Department</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Research and Development</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Legal Department</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>procurement</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Department</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Operations Department</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Administration Department</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>public-relations</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>public-relations</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>PR Department</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Public Relations</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>quality-assurance</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>QA Department</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>facilities-management</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>facilities-management</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Facilities Department</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Facilities Management</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>training-and-development</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>training-and-development</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Training Department</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Training and Development</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>HumanAgentId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Mbox</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>agent-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>agent_001</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Alice Johnson</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>alice.johnson@example.com</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>agent-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>agent_002</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Brian Smith</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>brian.smith@example.com</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>agent-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>agent_003</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Catherine Lee</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>catherine.lee@example.com</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>agent-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>agent_004</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>David Kim</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>david.kim@example.com</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>agent-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>agent_005</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Emily Chen</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>emily.chen@example.com</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>agent-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>agent_006</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Frank Miller</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>frank.miller@example.com</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>agent-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>agent_007</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Grace Park</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>grace.park@example.com</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>agent-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>agent_008</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Henry Adams</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>henry.adams@example.com</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>agent-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>agent_009</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Isabella Martinez</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>isabella.martinez@example.com</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>agent-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>agent_010</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Jack Wilson</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>jack.wilson@example.com</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>agent-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>agent_011</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Karen Patel</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>karen.patel@example.com</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>agent-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>agent_012</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Liam Nguyen</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>liam.nguyen@example.com</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>agent-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>agent_013</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Monica Rivera</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>monica.rivera@example.com</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>agent-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>agent_014</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nathan Brown</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>nathan.brown@example.com</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>agent-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>agent_015</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Olivia Clark</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>olivia.clark@example.com</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CustomerId</t>
+          <t>AIAgentId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>EmailAddress</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>FirstName</t>
+          <t>DisplayName</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>LastName</t>
+          <t>ModelVersion</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>FullName</t>
+          <t>Roles</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cust0001</t>
+          <t>ava</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CUST0001</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>jane.smith@email.com</t>
+          <t>CustomerSupportBot</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Smith, Jane</t>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cust0002</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CUST0002</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>john.doe@email.com</t>
+          <t>SalesAssistantAI</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Doe</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Doe, John</t>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cust0003</t>
+          <t>maya</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CUST0003</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>emily.jones@email.com</t>
+          <t>HRRecruiterBot</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jones</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Jones, Emily</t>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Eli</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>FinanceAdvisorAI</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Eli</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>zara</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Zara</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>MarketingCopyAI</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Zara</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>owen</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>LegalDraftBot</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>nina</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>MedicalAssistantAI</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>kai</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Kai</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>TravelPlannerBot</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Kai</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>sophie</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EcommerceHelperAI</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EducationTutorBot</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>liam</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>RealEstateAdvisorAI</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>jade</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Jade</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>FitnessCoachBot</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Jade</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>mila</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Mila</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>EventPlannerAI</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Mila</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>noah</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>PersonalFinanceBot</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>GPT-3.5</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ella</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ContentEditorAI</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>GPT-4.0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AutomatedPipelineId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DisplayName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>lead-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>lead-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Salesforce to Slack Lead Alert</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Lead Notification Pipeline</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>e-commerce-order-sync</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>e-commerce-order-sync</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Shopify Order to QuickBooks Invoice</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>E-commerce Order Sync</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>editor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>issue-tracking-bridge</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>issue-tracking-bridge</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Jira Issue to Trello Card</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Issue Tracking Bridge</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>newsletter-signup-sync</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>newsletter-signup-sync</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Google Sheets to Mailchimp Subscriber</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter Signup Sync</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>moderator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>support-ticket-automation</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>support-ticket-automation</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Zendesk Ticket to Asana Task</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Support Ticket Automation</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>devops-integration</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>devops-integration</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>GitHub PR to Jira Story</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>DevOps Integration</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>finance-automation</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>finance-automation</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Stripe Payment to Xero Invoice</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Finance Automation</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>project-intake-pipeline</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>project-intake-pipeline</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Airtable Form to Monday.com Item</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Project Intake Pipeline</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>crm-data-sync</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>crm-data-sync</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>HubSpot Contact to Salesforce Lead</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>CRM Data Sync</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>calendar-integration</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>calendar-integration</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Google Calendar Event to Teams Meeting</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Calendar Integration</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-pipeline</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-pipeline</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Typeform Response to Notion Database</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Survey Data Pipeline</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>task-management-sync</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>task-management-sync</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Trello Card to Google Tasks</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Task Management Sync</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>cloud-storage-sync</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>cloud-storage-sync</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Dropbox Upload to Google Drive</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Storage Sync</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>email-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>email-notification-pipeline</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Outlook Email to Slack Channel</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Email Notification Pipeline</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-export</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>survey-data-export</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>SurveyMonkey Response to Excel Sheet</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Survey Data Export</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>owner</t>
         </is>
       </c>
     </row>

--- a/execution-substrates/csv/rulebook.xlsx
+++ b/execution-substrates/csv/rulebook.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Smith, Jane</t>
+          <t>Jane Smith</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Doe, John</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Jones, Emily</t>
+          <t>Emily Jones</t>
         </is>
       </c>
     </row>

--- a/execution-substrates/csv/rulebook.xlsx
+++ b/execution-substrates/csv/rulebook.xlsx
@@ -1,13 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TypesOfProject" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -149,6 +153,41 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Identifier for the customers.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Thec ustomers email address</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>First Name of the customer - used to make the full name</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Last Name of the customer - used to make the full name</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Full name is computed from the first and last name of the customer</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -454,7 +493,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CustomerId</t>
+          <t>ClientId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -496,12 +535,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>jane.smith@email.com</t>
+          <t>larry.smith@email.com</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Bob</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -509,10 +548,9 @@
           <t>Smith</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Jane Smith</t>
-        </is>
+      <c r="F2" s="3">
+        <f>$D2 &amp; " " &amp; $E2</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -541,10 +579,9 @@
           <t>Doe</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>John Doe</t>
-        </is>
+      <c r="F3" s="3">
+        <f>$D3 &amp; " " &amp; $E3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -573,10 +610,811 @@
           <t>Jones</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Emily Jones</t>
-        </is>
+      <c r="F4" s="3">
+        <f>$D4 &amp; " " &amp; $E4</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ProjectId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ProjectType</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ProjectTypeName</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ProjectTypeDescription</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ProjectTypeRequiresManagerApproval</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DueDate</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>IsApproved</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovedBy</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovedByRoleIsManager</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovedByName</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovedByEmailAddress</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ApprovedByPhoneNumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>internal-tools-dashboard</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Internal Tools Dashboard</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Build internal analytics dashboard for team productivity metrics</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>An internal project that is not publicly accessible</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>sarah-chen</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Chen</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>sarah.chen@acmecorp.example</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>555-0101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>customer-portal-redesign</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Customer Portal Redesign</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Complete redesign of customer-facing portal with modern UX</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>clientfacing</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>ClientFacing</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Open, public facing communication</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>priya-patel</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>priya.patel@acmecorp.example</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>555-0103</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>gdpr-compliance-audit</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>GDPR Compliance Audit</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Annual compliance audit and documentation update</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>compliance</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>mike-johnson</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Mike Johnson</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>mike.johnson@acmecorp.example</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>555-0102</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>EmailAddress</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>PhoneNumber</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RoleName</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RoleDescription</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Projects</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>RoleIsManager</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>sarah-chen</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Chen</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>sarah.chen@acmecorp.example</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>555-0101</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>projectmanager</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ProjectManager</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>The project Manager makes sure that the developers do what the analysts ask for</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>internal-tools-dashboard</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>mike-johnson</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Mike Johnson</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>mike.johnson@acmecorp.example</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>555-0102</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Developers handle the implementation and are responsible for making the final product do what is expected</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>gdpr-compliance-audit</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>priya-patel</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Priya Patel</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>priya.patel@acmecorp.example</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>555-0103</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>The business analysis know what the customer's want.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>customer-portal-redesign</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RoleId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>IsManager</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CountOfEmployees</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Developers handle the implementation and are responsible for making the final product do what is expected</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>mike-johnson</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>projectmanager</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ProjectManager</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>The project Manager makes sure that the developers do what the analysts ask for</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>sarah-chen</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>The business analysis know what the customer's want.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>priya-patel</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TypesOfProjectId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>RequiresManagerApproval</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Projects</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CountOfProjects</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>An internal project that is not publicly accessible</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>internal-tools-dashboard</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>clientfacing</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ClientFacing</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Open, public facing communication</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>customer-portal-redesign</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>compliance</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>gdpr-compliance-audit</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/execution-substrates/csv/rulebook.xlsx
+++ b/execution-substrates/csv/rulebook.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cust0001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CUST0001</t>
+          <t>jane-smith-email-com</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>jane.smith-email.com</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Bob</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -511,19 +511,19 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Jane Smith</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cust0002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>CUST0002</t>
+          <t>john-doe-email-com</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>john.doe-email.com</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -543,19 +543,19 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>John Doe</t>
+          <t>Jimmy Doe</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cust0003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CUST0003</t>
+          <t>emily-jones-email-com</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>emily.jones-email.com</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Emily Jones</t>
+          <t>Mary Jones</t>
         </is>
       </c>
     </row>

--- a/execution-substrates/csv/rulebook.xlsx
+++ b/execution-substrates/csv/rulebook.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TypesOfProject" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBVersions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBCustomizations" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -493,12 +491,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClientId</t>
+          <t>CustomerId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -525,22 +523,21 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cust0001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CUST0001</t>
-        </is>
+          <t>jane-smith-email-com</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE($C2, "@", "-")</f>
+        <v/>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>larry.smith@email.com</t>
+          <t>jane.smith@email.com</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Bob</t>
+          <t>Bobby</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -549,20 +546,19 @@
         </is>
       </c>
       <c r="F2" s="3">
-        <f>$D2 &amp; " " &amp; $E2</f>
+        <f>$E2 &amp; ", " &amp; $D2</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cust0002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>CUST0002</t>
-        </is>
+          <t>john-doe-email-com</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE($C3, "@", "-")</f>
+        <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -571,7 +567,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -580,20 +576,19 @@
         </is>
       </c>
       <c r="F3" s="3">
-        <f>$D3 &amp; " " &amp; $E3</f>
+        <f>$E3 &amp; ", " &amp; $D3</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cust0003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CUST0003</t>
-        </is>
+          <t>emily-jones-email-com</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE($C4, "@", "-")</f>
+        <v/>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -602,7 +597,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -611,7 +606,7 @@
         </is>
       </c>
       <c r="F4" s="3">
-        <f>$D4 &amp; " " &amp; $E4</f>
+        <f>$E4 &amp; ", " &amp; $D4</f>
         <v/>
       </c>
     </row>
@@ -627,292 +622,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ProjectId</t>
+          <t>ERBVersionId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>BaseId</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ProjectType</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ProjectTypeName</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ProjectTypeDescription</t>
+          <t>CommitDate</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ProjectTypeRequiresManagerApproval</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>DueDate</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>IsApproved</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ApprovedBy</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>ApprovedByRoleIsManager</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ApprovedByName</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>ApprovedByEmailAddress</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>ApprovedByPhoneNumber</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>internal-tools-dashboard</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Internal Tools Dashboard</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Build internal analytics dashboard for team productivity metrics</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>An internal project that is not publicly accessible</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>sarah-chen</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Sarah Chen</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>sarah.chen@acmecorp.example</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>555-0101</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>customer-portal-redesign</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Customer Portal Redesign</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Complete redesign of customer-facing portal with modern UX</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>clientfacing</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>ClientFacing</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Open, public facing communication</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>priya-patel</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Priya Patel</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>priya.patel@acmecorp.example</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>555-0103</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>gdpr-compliance-audit</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>GDPR Compliance Audit</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Annual compliance audit and documentation update</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>compliance</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>mike-johnson</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Mike Johnson</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>mike.johnson@acmecorp.example</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>555-0102</t>
+          <t>IsPublished</t>
         </is>
       </c>
     </row>
@@ -927,24 +682,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>EmployeeId</t>
+          <t>ERBCustomizationId</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -954,467 +706,254 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>EmailAddress</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>PhoneNumber</t>
+          <t>SQLCode</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>SQLTarget</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>RoleName</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>RoleDescription</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Projects</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>RoleIsManager</t>
+          <t>CustomizationType</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>sarah-chen</t>
+          <t>03a-customize-schema-sql</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Sarah Chen</t>
+          <t>03a-customize-schema.sql</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sarah.chen@acmecorp.example</t>
+          <t>Customize Schema</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>555-0101</t>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE SCHEMA - User-defined tables and schema modifications
+-- ============================================================================
+-- This file is for YOUR custom schema changes that should persist across
+-- regeneration of the base ERB files.
+--
+-- USE THIS FILE FOR:
+--   - Additional tables not defined in the rulebook
+--   - Extra columns on existing tables (ALTER TABLE)
+--   - Custom indexes for performance tuning
+--   - Custom constraints or triggers
+--
+-- IMPORTANT:
+--   - This file runs AFTER 01-drop-and-create-tables.sql
+--   - The base tables already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom schema changes go here:
+</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>projectmanager</t>
+          <t>Postgres</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ProjectManager</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>The project Manager makes sure that the developers do what the analysts ask for</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>internal-tools-dashboard</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
+          <t>Schema</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>mike-johnson</t>
+          <t>03b-customize-functions-sql</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Mike Johnson</t>
+          <t>03b-customize-functions.sql</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>mike.johnson@acmecorp.example</t>
+          <t>Customize Functions</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>555-0102</t>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE FUNCTIONS - User-defined calculation functions
+-- ============================================================================
+-- This file is for YOUR custom PostgreSQL functions that should persist
+-- across regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 02-create-functions.sql
+--   - Base ERB calc functions already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom functions go here:
+</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>developer</t>
+          <t>Postgres</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Developers handle the implementation and are responsible for making the final product do what is expected</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>gdpr-compliance-audit</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
+          <t>Functions</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>priya-patel</t>
+          <t>03c-customize-views-sql</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>03c-customize-views.sql</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>priya.patel@acmecorp.example</t>
+          <t>Customize Views</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>555-0103</t>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE VIEWS - User-defined views and view extensions
+-- ============================================================================
+-- This file is for YOUR custom views that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 03-create-views.sql
+--   - All base vw_* views already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom views go here:
+</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>analyst</t>
+          <t>Postgres</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>The business analysis know what the customer's want.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>customer-portal-redesign</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>RoleId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>IsManager</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Employees</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CountOfEmployees</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>developer</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Developers handle the implementation and are responsible for making the final product do what is expected</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>mike-johnson</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>projectmanager</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>ProjectManager</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>The project Manager makes sure that the developers do what the analysts ask for</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>sarah-chen</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>The business analysis know what the customer's want.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>priya-patel</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TypesOfProjectId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>RequiresManagerApproval</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Projects</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CountOfProjects</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>An internal project that is not publicly accessible</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>internal-tools-dashboard</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>clientfacing</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>ClientFacing</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Open, public facing communication</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>customer-portal-redesign</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
+          <t>Views</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>compliance</t>
+          <t>03d-customize-rls-sql</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="b">
-        <v>1</v>
+          <t>03d-customize-rls.sql</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Customize Policies (RLS)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE POLICIES - User-defined Row Level Security policies
+-- ============================================================================
+-- This file is for YOUR custom RLS policies that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 04-create-policies.sql
+--   - Base RLS policies already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom policies go here:
+</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>gdpr-compliance-audit</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>1</v>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>RLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>03e-customize-data-sql</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>03e-customize-data.sql</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Customize Data (Seeds / Migrations)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE DATA - User-defined seed data and data migrations
+-- ============================================================================
+-- This file is for YOUR custom seed data that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 05-insert-data.sql
+--   - Base seed data already exists when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom data inserts go here:
+</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/execution-substrates/csv/rulebook.xlsx
+++ b/execution-substrates/csv/rulebook.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBVersions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBCustomizations" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +494,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Customer</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -523,12 +521,13 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>jane-smith-email-com</t>
-        </is>
-      </c>
-      <c r="B2" s="3">
-        <f>SUBSTITUTE($C2, "@", "-")</f>
-        <v/>
+          <t>cust0001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>CUST0001</t>
+        </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -537,7 +536,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Bobby</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -553,12 +552,13 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>john-doe-email-com</t>
-        </is>
-      </c>
-      <c r="B3" s="3">
-        <f>SUBSTITUTE($C3, "@", "-")</f>
-        <v/>
+          <t>cust0002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CUST0002</t>
+        </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Jimmy</t>
+          <t>John</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -583,12 +583,13 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>emily-jones-email-com</t>
-        </is>
-      </c>
-      <c r="B4" s="3">
-        <f>SUBSTITUTE($C4, "@", "-")</f>
-        <v/>
+          <t>cust0003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CUST0003</t>
+        </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -597,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -614,349 +615,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ERBVersionId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>BaseId</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CommitDate</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>IsPublished</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ERBCustomizationId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>SQLCode</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>SQLTarget</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CustomizationType</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>03a-customize-schema-sql</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>03a-customize-schema.sql</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Customize Schema</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE SCHEMA - User-defined tables and schema modifications
--- ============================================================================
--- This file is for YOUR custom schema changes that should persist across
--- regeneration of the base ERB files.
---
--- USE THIS FILE FOR:
---   - Additional tables not defined in the rulebook
---   - Extra columns on existing tables (ALTER TABLE)
---   - Custom indexes for performance tuning
---   - Custom constraints or triggers
---
--- IMPORTANT:
---   - This file runs AFTER 01-drop-and-create-tables.sql
---   - The base tables already exist when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom schema changes go here:
-</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Schema</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>03b-customize-functions-sql</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>03b-customize-functions.sql</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Customize Functions</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE FUNCTIONS - User-defined calculation functions
--- ============================================================================
--- This file is for YOUR custom PostgreSQL functions that should persist
--- across regeneration of the base ERB files.
---
--- IMPORTANT:
---   - This file runs AFTER 02-create-functions.sql
---   - Base ERB calc functions already exist when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom functions go here:
-</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Functions</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>03c-customize-views-sql</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>03c-customize-views.sql</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Customize Views</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE VIEWS - User-defined views and view extensions
--- ============================================================================
--- This file is for YOUR custom views that should persist across
--- regeneration of the base ERB files.
---
--- IMPORTANT:
---   - This file runs AFTER 03-create-views.sql
---   - All base vw_* views already exist when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom views go here:
-</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Views</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>03d-customize-rls-sql</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>03d-customize-rls.sql</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Customize Policies (RLS)</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE POLICIES - User-defined Row Level Security policies
--- ============================================================================
--- This file is for YOUR custom RLS policies that should persist across
--- regeneration of the base ERB files.
---
--- IMPORTANT:
---   - This file runs AFTER 04-create-policies.sql
---   - Base RLS policies already exist when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom policies go here:
-</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>RLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>03e-customize-data-sql</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>03e-customize-data.sql</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Customize Data (Seeds / Migrations)</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-- ============================================================================
--- CUSTOMIZE DATA - User-defined seed data and data migrations
--- ============================================================================
--- This file is for YOUR custom seed data that should persist across
--- regeneration of the base ERB files.
---
--- IMPORTANT:
---   - This file runs AFTER 05-insert-data.sql
---   - Base seed data already exists when this runs
---   - This file will NOT be overwritten by ERB regeneration
---
--- ============================================================================
--- Your custom data inserts go here:
-</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Postgres</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/execution-substrates/csv/rulebook.xlsx
+++ b/execution-substrates/csv/rulebook.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBVersions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBCustomizations" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +496,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -521,13 +523,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cust0001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CUST0001</t>
-        </is>
+          <t>jane-smith-email-com</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUBSTITUTE($C2, "@", "-")</f>
+        <v/>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -536,7 +537,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Bobby</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -552,13 +553,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>cust0002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>CUST0002</t>
-        </is>
+          <t>john-doe-email-com</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUBSTITUTE($C3, "@", "-")</f>
+        <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -583,13 +583,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>cust0003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CUST0003</t>
-        </is>
+          <t>emily-jones-email-com</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>SUBSTITUTE($C4, "@", "-")</f>
+        <v/>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -598,7 +597,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -615,4 +614,349 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ERBVersionId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>BaseId</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CommitDate</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>IsPublished</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ERBCustomizationId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>SQLCode</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SQLTarget</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CustomizationType</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>03a-customize-schema-sql</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>03a-customize-schema.sql</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Customize Schema</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE SCHEMA - User-defined tables and schema modifications
+-- ============================================================================
+-- This file is for YOUR custom schema changes that should persist across
+-- regeneration of the base ERB files.
+--
+-- USE THIS FILE FOR:
+--   - Additional tables not defined in the rulebook
+--   - Extra columns on existing tables (ALTER TABLE)
+--   - Custom indexes for performance tuning
+--   - Custom constraints or triggers
+--
+-- IMPORTANT:
+--   - This file runs AFTER 01-drop-and-create-tables.sql
+--   - The base tables already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom schema changes go here:
+</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>03b-customize-functions-sql</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>03b-customize-functions.sql</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Customize Functions</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE FUNCTIONS - User-defined calculation functions
+-- ============================================================================
+-- This file is for YOUR custom PostgreSQL functions that should persist
+-- across regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 02-create-functions.sql
+--   - Base ERB calc functions already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom functions go here:
+</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>03c-customize-views-sql</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>03c-customize-views.sql</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Customize Views</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE VIEWS - User-defined views and view extensions
+-- ============================================================================
+-- This file is for YOUR custom views that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 03-create-views.sql
+--   - All base vw_* views already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom views go here:
+</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Views</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>03d-customize-rls-sql</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>03d-customize-rls.sql</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Customize Policies (RLS)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE POLICIES - User-defined Row Level Security policies
+-- ============================================================================
+-- This file is for YOUR custom RLS policies that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 04-create-policies.sql
+--   - Base RLS policies already exist when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom policies go here:
+</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>RLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>03e-customize-data-sql</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>03e-customize-data.sql</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Customize Data (Seeds / Migrations)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-- ============================================================================
+-- CUSTOMIZE DATA - User-defined seed data and data migrations
+-- ============================================================================
+-- This file is for YOUR custom seed data that should persist across
+-- regeneration of the base ERB files.
+--
+-- IMPORTANT:
+--   - This file runs AFTER 05-insert-data.sql
+--   - Base seed data already exists when this runs
+--   - This file will NOT be overwritten by ERB regeneration
+--
+-- ============================================================================
+-- Your custom data inserts go here:
+</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Postgres</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>